--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -2,16 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Progress_Data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Daily_Log" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -29,22 +28,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -57,37 +60,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEEFF"/>
+        <fgColor rgb="FFDDEEFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFDE7"/>
+        <fgColor rgb="FFFFFDE7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDFFEE"/>
+        <fgColor rgb="FFDDFFEE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FDEBD0"/>
+        <fgColor rgb="FFFDEBD0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00375623"/>
+        <fgColor rgb="FF375623"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,23 +104,48 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </left>
       <right style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </right>
       <top style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </top>
       <bottom style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -125,115 +153,92 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </right>
       <top style="thin">
-        <color rgb="00AAAAAA"/>
+        <color rgb="FFAAAAAA"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00AAAAAA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00AAAAAA"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00AAAAAA"/>
-      </right>
-      <top style="thin">
-        <color rgb="00AAAAAA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00AAAAAA"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -599,18 +604,18 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" style="21" min="1" max="1"/>
+    <col width="28" customWidth="1" style="21" min="2" max="2"/>
+    <col width="16" customWidth="1" style="21" min="3" max="3"/>
+    <col width="22" customWidth="1" style="21" min="4" max="4"/>
+    <col width="16" customWidth="1" style="21" min="5" max="5"/>
+    <col width="20" customWidth="1" style="21" min="6" max="6"/>
+    <col width="14" customWidth="1" style="21" min="7" max="7"/>
+    <col width="12" customWidth="1" style="21" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="26.1" customHeight="1" s="21">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>MARGALLA ENCLAVE LINK ROAD — EARTHWORK FILL PROGRESS  |  Gross: 898,453 m³  −  Structure: 57,294 m³  =  Net Target: 841,159 m³</t>
         </is>
@@ -623,214 +628,214 @@
       <c r="G1" s="23" t="n"/>
       <c r="H1" s="24" t="n"/>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="21.95" customHeight="1" s="21">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Total Qty (m³)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Work Done To Date (m³)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Daily Added (m³)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Total Work Done (m³)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Balance (m³)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>Progress (%)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Al Ajal Builders</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Section-1 (0+000 to 1+000)</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="4" t="n">
         <v>242029</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="5" t="n">
         <v>134499</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <f>D3+E3</f>
         <v/>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <f>MAX(0,C3-F3)</f>
         <v/>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <f>IF(C3&gt;0,F3/C3,0)</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>BAS Construction</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Section-2 (1+000 to 2+000)</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n">
+      <c r="C4" s="11" t="n">
         <v>349638</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="5" t="n">
         <v>195170</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <f>D4+E4</f>
         <v/>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <f>MAX(0,C4-F4)</f>
         <v/>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="8">
         <f>IF(C4&gt;0,F4/C4,0)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>M. Shehzad Abbasi</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Section-3 (2+000 to 3+000)</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="5" t="n">
         <v>211523</v>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>153071</v>
-      </c>
-      <c r="E5" s="6" t="n">
+      <c r="D5" s="5" t="n">
+        <v>123470</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <f>D5+E5</f>
         <v/>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <f>MAX(0,C5-F5)</f>
         <v/>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <f>IF(C5&gt;0,F5/C5,0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Fazal Rehman</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Section-4 (3+000 to 3+750)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="16" t="n">
         <v>95263</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="5" t="n">
         <v>42352</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <f>D6+E6</f>
         <v/>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="7">
         <f>MAX(0,C6-F6)</f>
         <v/>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <f>IF(C6&gt;0,F6/C6,0)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="19">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="18">
         <f>SUM(C3:C6)</f>
         <v/>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="18">
         <f>SUM(D3:D6)</f>
         <v/>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="18">
         <f>SUM(E3:E6)</f>
         <v/>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="18">
         <f>SUM(F3:F6)</f>
         <v/>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="18">
         <f>SUM(G3:G6)</f>
         <v/>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="19">
         <f>IF(C7&gt;0,F7/C7,0)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Structure Deduction: 57,294 m³  →  Net Target: 841,159 m³  |  Work Done: 525,092 m³  |  Net Balance: 316,067 m³  |  Net Progress: 62.4%</t>
         </is>
@@ -854,16 +859,16 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" style="21" min="1" max="1"/>
+    <col width="24" customWidth="1" style="21" min="2" max="2"/>
+    <col width="28" customWidth="1" style="21" min="3" max="3"/>
+    <col width="18" customWidth="1" style="21" min="4" max="4"/>
+    <col width="20" customWidth="1" style="21" min="5" max="5"/>
+    <col width="25" customWidth="1" style="21" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+    <row r="1" ht="26.1" customHeight="1" s="21">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>DAILY WORK LOG</t>
         </is>
@@ -875,32 +880,32 @@
       <c r="F1" s="24" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Contractor</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Daily Added (m³)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>Cumulative WD (m³)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -51,7 +51,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -93,8 +93,13 @@
         <fgColor rgb="FF375623"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFDE7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -161,11 +166,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -234,6 +253,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -685,10 +710,10 @@
         <v>242029</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>134499</v>
+        <v>134500</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6">
         <f>D3+E3</f>
@@ -718,10 +743,10 @@
         <v>349638</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>195170</v>
+        <v>195171</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6">
         <f>D4+E4</f>
@@ -751,10 +776,10 @@
         <v>211523</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>123470</v>
+        <v>123471</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -784,10 +809,10 @@
         <v>95263</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>42352</v>
+        <v>42353</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>
@@ -856,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="21" min="1" max="1"/>
@@ -911,6 +936,102 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t>Al Ajal Builders</t>
+        </is>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>Section-1 (0+000 to 1+000)</t>
+        </is>
+      </c>
+      <c r="D3" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="27" t="n">
+        <v>134500</v>
+      </c>
+      <c r="F3" s="26" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B4" s="26" t="inlineStr">
+        <is>
+          <t>BAS Construction</t>
+        </is>
+      </c>
+      <c r="C4" s="26" t="inlineStr">
+        <is>
+          <t>Section-2 (1+000 to 2+000)</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="27" t="n">
+        <v>195171</v>
+      </c>
+      <c r="F4" s="26" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="inlineStr">
+        <is>
+          <t>M. Shehzad Abbasi</t>
+        </is>
+      </c>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t>Section-3 (2+000 to 3+000)</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>123471</v>
+      </c>
+      <c r="F5" s="26" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t>Fazal Rehman</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>Section-4 (3+000 to 3+750)</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>42353</v>
+      </c>
+      <c r="F6" s="26" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -710,10 +710,10 @@
         <v>242029</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>134500</v>
+        <v>137900</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1</v>
+        <v>3400</v>
       </c>
       <c r="F3" s="6">
         <f>D3+E3</f>
@@ -743,10 +743,10 @@
         <v>349638</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>195171</v>
+        <v>199971</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>4800</v>
       </c>
       <c r="F4" s="6">
         <f>D4+E4</f>
@@ -776,10 +776,10 @@
         <v>211523</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>123471</v>
+        <v>126171</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2700</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -809,10 +809,10 @@
         <v>95263</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>42353</v>
+        <v>44153</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>1800</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>
@@ -881,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="21" min="1" max="1"/>
@@ -1032,6 +1032,102 @@
       </c>
       <c r="F6" s="26" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="inlineStr">
+        <is>
+          <t>Al Ajal Builders</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>Section-1 (0+000 to 1+000)</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>3400</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>137900</v>
+      </c>
+      <c r="F7" s="26" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>BAS Construction</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>Section-2 (1+000 to 2+000)</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="n">
+        <v>4800</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>199971</v>
+      </c>
+      <c r="F8" s="26" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="inlineStr">
+        <is>
+          <t>M. Shehzad Abbasi</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Section-3 (2+000 to 3+000)</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>126171</v>
+      </c>
+      <c r="F9" s="26" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Fazal Rehman</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Section-4 (3+000 to 3+750)</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>44153</v>
+      </c>
+      <c r="F10" s="26" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -710,10 +710,10 @@
         <v>242029</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>137900</v>
+        <v>141152</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>3400</v>
+        <v>3252</v>
       </c>
       <c r="F3" s="6">
         <f>D3+E3</f>
@@ -743,10 +743,10 @@
         <v>349638</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>199971</v>
+        <v>204971</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="F4" s="6">
         <f>D4+E4</f>
@@ -776,10 +776,10 @@
         <v>211523</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>126171</v>
+        <v>129071</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -809,10 +809,10 @@
         <v>95263</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>44153</v>
+        <v>46053</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>
@@ -881,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="21" min="1" max="1"/>
@@ -1128,6 +1128,102 @@
       </c>
       <c r="F10" s="26" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Al Ajal Builders</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>Section-1 (0+000 to 1+000)</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>3252</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>141152</v>
+      </c>
+      <c r="F11" s="26" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>BAS Construction</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Section-2 (1+000 to 2+000)</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E12" s="27" t="n">
+        <v>204971</v>
+      </c>
+      <c r="F12" s="26" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>M. Shehzad Abbasi</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Section-3 (2+000 to 3+000)</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>129071</v>
+      </c>
+      <c r="F13" s="26" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Fazal Rehman</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>Section-4 (3+000 to 3+750)</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="n">
+        <v>1900</v>
+      </c>
+      <c r="E14" s="27" t="n">
+        <v>46053</v>
+      </c>
+      <c r="F14" s="26" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -713,7 +713,7 @@
         <v>141152</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>3252</v>
+        <v>0</v>
       </c>
       <c r="F3" s="6">
         <f>D3+E3</f>
@@ -746,7 +746,7 @@
         <v>204971</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="F4" s="6">
         <f>D4+E4</f>
@@ -779,7 +779,7 @@
         <v>129071</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2900</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -812,7 +812,7 @@
         <v>46053</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -710,10 +710,10 @@
         <v>242029</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>141152</v>
+        <v>142652</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F3" s="6">
         <f>D3+E3</f>
@@ -743,10 +743,10 @@
         <v>349638</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>204971</v>
+        <v>209471</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>4500</v>
       </c>
       <c r="F4" s="6">
         <f>D4+E4</f>
@@ -776,10 +776,10 @@
         <v>211523</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>129071</v>
+        <v>131871</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -809,10 +809,10 @@
         <v>95263</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>46053</v>
+        <v>47853</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>
@@ -881,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="21" min="1" max="1"/>
@@ -1224,6 +1224,102 @@
       </c>
       <c r="F14" s="26" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Al Ajal Builders</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>Section-1 (0+000 to 1+000)</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E15" s="27" t="n">
+        <v>142652</v>
+      </c>
+      <c r="F15" s="26" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>BAS Construction</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Section-2 (1+000 to 2+000)</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E16" s="27" t="n">
+        <v>209471</v>
+      </c>
+      <c r="F16" s="26" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>M. Shehzad Abbasi</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>Section-3 (2+000 to 3+000)</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>131871</v>
+      </c>
+      <c r="F17" s="26" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>Fazal Rehman</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>Section-4 (3+000 to 3+750)</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E18" s="27" t="n">
+        <v>47853</v>
+      </c>
+      <c r="F18" s="26" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -713,7 +713,7 @@
         <v>142652</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="F3" s="6">
         <f>D3+E3</f>
@@ -746,7 +746,7 @@
         <v>209471</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4500</v>
+        <v>0</v>
       </c>
       <c r="F4" s="6">
         <f>D4+E4</f>
@@ -779,7 +779,7 @@
         <v>131871</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -812,7 +812,7 @@
         <v>47853</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -710,10 +710,10 @@
         <v>242029</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>142652</v>
+        <v>145052</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="F3" s="6">
         <f>D3+E3</f>
@@ -743,10 +743,10 @@
         <v>349638</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>209471</v>
+        <v>214471</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F4" s="6">
         <f>D4+E4</f>
@@ -776,10 +776,10 @@
         <v>211523</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>131871</v>
+        <v>134471</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -809,10 +809,10 @@
         <v>95263</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>47853</v>
+        <v>48993</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>
@@ -881,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="21" min="1" max="1"/>
@@ -1320,6 +1320,102 @@
       </c>
       <c r="F18" s="26" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>Al Ajal Builders</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>Section-1 (0+000 to 1+000)</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E19" s="27" t="n">
+        <v>145052</v>
+      </c>
+      <c r="F19" s="26" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>BAS Construction</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Section-2 (1+000 to 2+000)</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E20" s="27" t="n">
+        <v>214471</v>
+      </c>
+      <c r="F20" s="26" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>M. Shehzad Abbasi</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Section-3 (2+000 to 3+000)</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E21" s="27" t="n">
+        <v>134471</v>
+      </c>
+      <c r="F21" s="26" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Fazal Rehman</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Section-4 (3+000 to 3+750)</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="n">
+        <v>1140</v>
+      </c>
+      <c r="E22" s="27" t="n">
+        <v>48993</v>
+      </c>
+      <c r="F22" s="26" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -710,10 +710,10 @@
         <v>242029</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>145052</v>
+        <v>148052</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="F3" s="6">
         <f>D3+E3</f>
@@ -746,7 +746,7 @@
         <v>214471</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="F4" s="6">
         <f>D4+E4</f>
@@ -776,10 +776,10 @@
         <v>211523</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>134471</v>
+        <v>137321</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2600</v>
+        <v>2850</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -809,10 +809,10 @@
         <v>95263</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>48993</v>
+        <v>49973</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1140</v>
+        <v>980</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>
@@ -881,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="21" min="1" max="1"/>
@@ -1416,6 +1416,78 @@
       </c>
       <c r="F22" s="26" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Al Ajal Builders</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Section-1 (0+000 to 1+000)</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E23" s="27" t="n">
+        <v>148052</v>
+      </c>
+      <c r="F23" s="26" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>M. Shehzad Abbasi</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Section-3 (2+000 to 3+000)</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="n">
+        <v>2850</v>
+      </c>
+      <c r="E24" s="27" t="n">
+        <v>137321</v>
+      </c>
+      <c r="F24" s="26" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Fazal Rehman</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Section-4 (3+000 to 3+750)</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="n">
+        <v>980</v>
+      </c>
+      <c r="E25" s="27" t="n">
+        <v>49973</v>
+      </c>
+      <c r="F25" s="26" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -95,7 +95,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFDE7"/>
+        <fgColor rgb="FFFFFDE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -147,6 +147,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -166,25 +181,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00AAAAAA"/>
-      </left>
-      <right style="thin">
-        <color rgb="00AAAAAA"/>
-      </right>
-      <top style="thin">
-        <color rgb="00AAAAAA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00AAAAAA"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -241,6 +242,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -255,10 +262,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -629,31 +636,31 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="21" min="1" max="1"/>
-    <col width="28" customWidth="1" style="21" min="2" max="2"/>
-    <col width="16" customWidth="1" style="21" min="3" max="3"/>
-    <col width="22" customWidth="1" style="21" min="4" max="4"/>
-    <col width="16" customWidth="1" style="21" min="5" max="5"/>
-    <col width="20" customWidth="1" style="21" min="6" max="6"/>
-    <col width="14" customWidth="1" style="21" min="7" max="7"/>
-    <col width="12" customWidth="1" style="21" min="8" max="8"/>
+    <col width="24" customWidth="1" style="23" min="1" max="1"/>
+    <col width="28" customWidth="1" style="23" min="2" max="2"/>
+    <col width="16" customWidth="1" style="23" min="3" max="3"/>
+    <col width="22" customWidth="1" style="23" min="4" max="4"/>
+    <col width="16" customWidth="1" style="23" min="5" max="5"/>
+    <col width="20" customWidth="1" style="23" min="6" max="6"/>
+    <col width="14" customWidth="1" style="23" min="7" max="7"/>
+    <col width="12" customWidth="1" style="23" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.1" customHeight="1" s="21">
-      <c r="A1" s="22" t="inlineStr">
+    <row r="1" ht="26.1" customHeight="1" s="23">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>MARGALLA ENCLAVE LINK ROAD — EARTHWORK FILL PROGRESS  |  Gross: 898,453 m³  −  Structure: 57,294 m³  =  Net Target: 841,159 m³</t>
         </is>
       </c>
-      <c r="B1" s="23" t="n"/>
-      <c r="C1" s="23" t="n"/>
-      <c r="D1" s="23" t="n"/>
-      <c r="E1" s="23" t="n"/>
-      <c r="F1" s="23" t="n"/>
-      <c r="G1" s="23" t="n"/>
-      <c r="H1" s="24" t="n"/>
-    </row>
-    <row r="2" ht="21.95" customHeight="1" s="21">
+      <c r="B1" s="25" t="n"/>
+      <c r="C1" s="25" t="n"/>
+      <c r="D1" s="25" t="n"/>
+      <c r="E1" s="25" t="n"/>
+      <c r="F1" s="25" t="n"/>
+      <c r="G1" s="25" t="n"/>
+      <c r="H1" s="26" t="n"/>
+    </row>
+    <row r="2" ht="21.95" customHeight="1" s="23">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Contractor</t>
@@ -713,7 +720,7 @@
         <v>148052</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="F3" s="6">
         <f>D3+E3</f>
@@ -779,7 +786,7 @@
         <v>137321</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2850</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -806,13 +813,13 @@
         </is>
       </c>
       <c r="C6" s="16" t="n">
-        <v>95263</v>
+        <v>97000</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>49973</v>
+        <v>20000</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>
@@ -860,7 +867,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>Structure Deduction: 57,294 m³  →  Net Target: 841,159 m³  |  Work Done: 525,092 m³  |  Net Balance: 316,067 m³  |  Net Progress: 62.4%</t>
         </is>
@@ -884,25 +891,25 @@
   <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="21" min="1" max="1"/>
-    <col width="24" customWidth="1" style="21" min="2" max="2"/>
-    <col width="28" customWidth="1" style="21" min="3" max="3"/>
-    <col width="18" customWidth="1" style="21" min="4" max="4"/>
-    <col width="20" customWidth="1" style="21" min="5" max="5"/>
-    <col width="25" customWidth="1" style="21" min="6" max="6"/>
+    <col width="13" customWidth="1" style="23" min="1" max="1"/>
+    <col width="24" customWidth="1" style="23" min="2" max="2"/>
+    <col width="28" customWidth="1" style="23" min="3" max="3"/>
+    <col width="18" customWidth="1" style="23" min="4" max="4"/>
+    <col width="20" customWidth="1" style="23" min="5" max="5"/>
+    <col width="25" customWidth="1" style="23" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.1" customHeight="1" s="21">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="26.1" customHeight="1" s="23">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>DAILY WORK LOG</t>
         </is>
       </c>
-      <c r="B1" s="23" t="n"/>
-      <c r="C1" s="23" t="n"/>
-      <c r="D1" s="23" t="n"/>
-      <c r="E1" s="23" t="n"/>
-      <c r="F1" s="24" t="n"/>
+      <c r="B1" s="25" t="n"/>
+      <c r="C1" s="25" t="n"/>
+      <c r="D1" s="25" t="n"/>
+      <c r="E1" s="25" t="n"/>
+      <c r="F1" s="26" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -937,556 +944,556 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Al Ajal Builders</t>
         </is>
       </c>
-      <c r="C3" s="26" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Section-1 (0+000 to 1+000)</t>
         </is>
       </c>
-      <c r="D3" s="27" t="n">
+      <c r="D3" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="27" t="n">
+      <c r="E3" s="21" t="n">
         <v>134500</v>
       </c>
-      <c r="F3" s="26" t="inlineStr"/>
+      <c r="F3" s="20" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>BAS Construction</t>
         </is>
       </c>
-      <c r="C4" s="26" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Section-2 (1+000 to 2+000)</t>
         </is>
       </c>
-      <c r="D4" s="27" t="n">
+      <c r="D4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="27" t="n">
+      <c r="E4" s="21" t="n">
         <v>195171</v>
       </c>
-      <c r="F4" s="26" t="inlineStr"/>
+      <c r="F4" s="20" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="26" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>M. Shehzad Abbasi</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>Section-3 (2+000 to 3+000)</t>
         </is>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="21" t="n">
         <v>123471</v>
       </c>
-      <c r="F5" s="26" t="inlineStr"/>
+      <c r="F5" s="20" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Fazal Rehman</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>Section-4 (3+000 to 3+750)</t>
         </is>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="21" t="n">
         <v>42353</v>
       </c>
-      <c r="F6" s="26" t="inlineStr"/>
+      <c r="F6" s="20" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Al Ajal Builders</t>
         </is>
       </c>
-      <c r="C7" s="26" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>Section-1 (0+000 to 1+000)</t>
         </is>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="21" t="n">
         <v>3400</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="21" t="n">
         <v>137900</v>
       </c>
-      <c r="F7" s="26" t="inlineStr"/>
+      <c r="F7" s="20" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>BAS Construction</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>Section-2 (1+000 to 2+000)</t>
         </is>
       </c>
-      <c r="D8" s="27" t="n">
+      <c r="D8" s="21" t="n">
         <v>4800</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="21" t="n">
         <v>199971</v>
       </c>
-      <c r="F8" s="26" t="inlineStr"/>
+      <c r="F8" s="20" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="26" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>M. Shehzad Abbasi</t>
         </is>
       </c>
-      <c r="C9" s="26" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>Section-3 (2+000 to 3+000)</t>
         </is>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="21" t="n">
         <v>2700</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="21" t="n">
         <v>126171</v>
       </c>
-      <c r="F9" s="26" t="inlineStr"/>
+      <c r="F9" s="20" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Fazal Rehman</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>Section-4 (3+000 to 3+750)</t>
         </is>
       </c>
-      <c r="D10" s="27" t="n">
+      <c r="D10" s="21" t="n">
         <v>1800</v>
       </c>
-      <c r="E10" s="27" t="n">
+      <c r="E10" s="21" t="n">
         <v>44153</v>
       </c>
-      <c r="F10" s="26" t="inlineStr"/>
+      <c r="F10" s="20" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="26" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Al Ajal Builders</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>Section-1 (0+000 to 1+000)</t>
         </is>
       </c>
-      <c r="D11" s="27" t="n">
+      <c r="D11" s="21" t="n">
         <v>3252</v>
       </c>
-      <c r="E11" s="27" t="n">
+      <c r="E11" s="21" t="n">
         <v>141152</v>
       </c>
-      <c r="F11" s="26" t="inlineStr"/>
+      <c r="F11" s="20" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>BAS Construction</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>Section-2 (1+000 to 2+000)</t>
         </is>
       </c>
-      <c r="D12" s="27" t="n">
+      <c r="D12" s="21" t="n">
         <v>5000</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="21" t="n">
         <v>204971</v>
       </c>
-      <c r="F12" s="26" t="inlineStr"/>
+      <c r="F12" s="20" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>M. Shehzad Abbasi</t>
         </is>
       </c>
-      <c r="C13" s="26" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>Section-3 (2+000 to 3+000)</t>
         </is>
       </c>
-      <c r="D13" s="27" t="n">
+      <c r="D13" s="21" t="n">
         <v>2900</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="21" t="n">
         <v>129071</v>
       </c>
-      <c r="F13" s="26" t="inlineStr"/>
+      <c r="F13" s="20" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Fazal Rehman</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>Section-4 (3+000 to 3+750)</t>
         </is>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="21" t="n">
         <v>1900</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="21" t="n">
         <v>46053</v>
       </c>
-      <c r="F14" s="26" t="inlineStr"/>
+      <c r="F14" s="20" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Al Ajal Builders</t>
         </is>
       </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>Section-1 (0+000 to 1+000)</t>
         </is>
       </c>
-      <c r="D15" s="27" t="n">
+      <c r="D15" s="21" t="n">
         <v>1500</v>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="21" t="n">
         <v>142652</v>
       </c>
-      <c r="F15" s="26" t="inlineStr"/>
+      <c r="F15" s="20" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>BAS Construction</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>Section-2 (1+000 to 2+000)</t>
         </is>
       </c>
-      <c r="D16" s="27" t="n">
+      <c r="D16" s="21" t="n">
         <v>4500</v>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="21" t="n">
         <v>209471</v>
       </c>
-      <c r="F16" s="26" t="inlineStr"/>
+      <c r="F16" s="20" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>M. Shehzad Abbasi</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>Section-3 (2+000 to 3+000)</t>
         </is>
       </c>
-      <c r="D17" s="27" t="n">
+      <c r="D17" s="21" t="n">
         <v>2800</v>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="21" t="n">
         <v>131871</v>
       </c>
-      <c r="F17" s="26" t="inlineStr"/>
+      <c r="F17" s="20" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Fazal Rehman</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>Section-4 (3+000 to 3+750)</t>
         </is>
       </c>
-      <c r="D18" s="27" t="n">
+      <c r="D18" s="21" t="n">
         <v>1800</v>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="21" t="n">
         <v>47853</v>
       </c>
-      <c r="F18" s="26" t="inlineStr"/>
+      <c r="F18" s="20" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Al Ajal Builders</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>Section-1 (0+000 to 1+000)</t>
         </is>
       </c>
-      <c r="D19" s="27" t="n">
+      <c r="D19" s="21" t="n">
         <v>2400</v>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="21" t="n">
         <v>145052</v>
       </c>
-      <c r="F19" s="26" t="inlineStr"/>
+      <c r="F19" s="20" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>BAS Construction</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>Section-2 (1+000 to 2+000)</t>
         </is>
       </c>
-      <c r="D20" s="27" t="n">
+      <c r="D20" s="21" t="n">
         <v>5000</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="21" t="n">
         <v>214471</v>
       </c>
-      <c r="F20" s="26" t="inlineStr"/>
+      <c r="F20" s="20" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="26" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>M. Shehzad Abbasi</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>Section-3 (2+000 to 3+000)</t>
         </is>
       </c>
-      <c r="D21" s="27" t="n">
+      <c r="D21" s="21" t="n">
         <v>2600</v>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E21" s="21" t="n">
         <v>134471</v>
       </c>
-      <c r="F21" s="26" t="inlineStr"/>
+      <c r="F21" s="20" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>Fazal Rehman</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>Section-4 (3+000 to 3+750)</t>
         </is>
       </c>
-      <c r="D22" s="27" t="n">
+      <c r="D22" s="21" t="n">
         <v>1140</v>
       </c>
-      <c r="E22" s="27" t="n">
+      <c r="E22" s="21" t="n">
         <v>48993</v>
       </c>
-      <c r="F22" s="26" t="inlineStr"/>
+      <c r="F22" s="20" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>Al Ajal Builders</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>Section-1 (0+000 to 1+000)</t>
         </is>
       </c>
-      <c r="D23" s="27" t="n">
+      <c r="D23" s="21" t="n">
         <v>3000</v>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="21" t="n">
         <v>148052</v>
       </c>
-      <c r="F23" s="26" t="inlineStr"/>
+      <c r="F23" s="20" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>M. Shehzad Abbasi</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>Section-3 (2+000 to 3+000)</t>
         </is>
       </c>
-      <c r="D24" s="27" t="n">
+      <c r="D24" s="21" t="n">
         <v>2850</v>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="21" t="n">
         <v>137321</v>
       </c>
-      <c r="F24" s="26" t="inlineStr"/>
+      <c r="F24" s="20" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Fazal Rehman</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>Section-4 (3+000 to 3+750)</t>
         </is>
       </c>
-      <c r="D25" s="27" t="n">
+      <c r="D25" s="21" t="n">
         <v>980</v>
       </c>
-      <c r="E25" s="27" t="n">
+      <c r="E25" s="21" t="n">
         <v>49973</v>
       </c>
-      <c r="F25" s="26" t="inlineStr"/>
+      <c r="F25" s="20" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -51,7 +51,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -98,8 +98,13 @@
         <fgColor rgb="FFFFFDE7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFDE7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -181,11 +186,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -266,6 +285,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -717,10 +742,10 @@
         <v>242029</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>148052</v>
+        <v>151786</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>3734</v>
       </c>
       <c r="F3" s="6">
         <f>D3+E3</f>
@@ -750,10 +775,10 @@
         <v>349638</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>214471</v>
+        <v>217671</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="F4" s="6">
         <f>D4+E4</f>
@@ -783,10 +808,10 @@
         <v>211523</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>137321</v>
+        <v>140171</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>2850</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -816,10 +841,10 @@
         <v>97000</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>20000</v>
+        <v>21140</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>
@@ -888,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="23" min="1" max="1"/>
@@ -1495,6 +1520,102 @@
       </c>
       <c r="F25" s="20" t="n"/>
     </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Al Ajal Builders</t>
+        </is>
+      </c>
+      <c r="C26" s="30" t="inlineStr">
+        <is>
+          <t>Section-1 (0+000 to 1+000)</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="n">
+        <v>3734</v>
+      </c>
+      <c r="E26" s="31" t="n">
+        <v>151786</v>
+      </c>
+      <c r="F26" s="30" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>BAS Construction</t>
+        </is>
+      </c>
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t>Section-2 (1+000 to 2+000)</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E27" s="31" t="n">
+        <v>217671</v>
+      </c>
+      <c r="F27" s="30" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>M. Shehzad Abbasi</t>
+        </is>
+      </c>
+      <c r="C28" s="30" t="inlineStr">
+        <is>
+          <t>Section-3 (2+000 to 3+000)</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="n">
+        <v>2850</v>
+      </c>
+      <c r="E28" s="31" t="n">
+        <v>140171</v>
+      </c>
+      <c r="F28" s="30" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Fazal Rehman</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>Section-4 (3+000 to 3+750)</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="n">
+        <v>1140</v>
+      </c>
+      <c r="E29" s="31" t="n">
+        <v>21140</v>
+      </c>
+      <c r="F29" s="30" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -745,7 +745,7 @@
         <v>151786</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>3734</v>
+        <v>0</v>
       </c>
       <c r="F3" s="6">
         <f>D3+E3</f>
@@ -778,7 +778,7 @@
         <v>217671</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="F4" s="6">
         <f>D4+E4</f>
@@ -811,7 +811,7 @@
         <v>140171</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2850</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -844,7 +844,7 @@
         <v>21140</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1140</v>
+        <v>0</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -742,10 +742,10 @@
         <v>242029</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>151786</v>
+        <v>155843</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>4057</v>
       </c>
       <c r="F3" s="6">
         <f>D3+E3</f>
@@ -775,10 +775,10 @@
         <v>349638</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>217671</v>
+        <v>221671</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F4" s="6">
         <f>D4+E4</f>
@@ -808,10 +808,10 @@
         <v>211523</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>140171</v>
+        <v>143371</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -841,10 +841,10 @@
         <v>97000</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>21140</v>
+        <v>22480</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1340</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>
@@ -913,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="23" min="1" max="1"/>
@@ -1616,6 +1616,102 @@
       </c>
       <c r="F29" s="30" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Al Ajal Builders</t>
+        </is>
+      </c>
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>Section-1 (0+000 to 1+000)</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="n">
+        <v>4057</v>
+      </c>
+      <c r="E30" s="31" t="n">
+        <v>155843</v>
+      </c>
+      <c r="F30" s="30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>BAS Construction</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="inlineStr">
+        <is>
+          <t>Section-2 (1+000 to 2+000)</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E31" s="31" t="n">
+        <v>221671</v>
+      </c>
+      <c r="F31" s="30" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>M. Shehzad Abbasi</t>
+        </is>
+      </c>
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <t>Section-3 (2+000 to 3+000)</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E32" s="31" t="n">
+        <v>143371</v>
+      </c>
+      <c r="F32" s="30" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B33" s="30" t="inlineStr">
+        <is>
+          <t>Fazal Rehman</t>
+        </is>
+      </c>
+      <c r="C33" s="30" t="inlineStr">
+        <is>
+          <t>Section-4 (3+000 to 3+750)</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="n">
+        <v>1340</v>
+      </c>
+      <c r="E33" s="31" t="n">
+        <v>22480</v>
+      </c>
+      <c r="F33" s="30" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -100,7 +100,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFDE7"/>
+        <fgColor rgb="FFFFFDE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -167,6 +167,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFAAAAAA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -185,20 +200,6 @@
       </top>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00AAAAAA"/>
-      </left>
-      <right style="thin">
-        <color rgb="00AAAAAA"/>
-      </right>
-      <top style="thin">
-        <color rgb="00AAAAAA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00AAAAAA"/>
-      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -269,28 +270,28 @@
     <xf numFmtId="3" fontId="0" fillId="9" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="10" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -661,31 +662,31 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="23" min="1" max="1"/>
-    <col width="28" customWidth="1" style="23" min="2" max="2"/>
-    <col width="16" customWidth="1" style="23" min="3" max="3"/>
-    <col width="22" customWidth="1" style="23" min="4" max="4"/>
-    <col width="16" customWidth="1" style="23" min="5" max="5"/>
-    <col width="20" customWidth="1" style="23" min="6" max="6"/>
-    <col width="14" customWidth="1" style="23" min="7" max="7"/>
-    <col width="12" customWidth="1" style="23" min="8" max="8"/>
+    <col width="24" customWidth="1" style="25" min="1" max="1"/>
+    <col width="28" customWidth="1" style="25" min="2" max="2"/>
+    <col width="16" customWidth="1" style="25" min="3" max="3"/>
+    <col width="22" customWidth="1" style="25" min="4" max="4"/>
+    <col width="16" customWidth="1" style="25" min="5" max="5"/>
+    <col width="20" customWidth="1" style="25" min="6" max="6"/>
+    <col width="14" customWidth="1" style="25" min="7" max="7"/>
+    <col width="12" customWidth="1" style="25" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.1" customHeight="1" s="23">
-      <c r="A1" s="28" t="inlineStr">
+    <row r="1" ht="26.1" customHeight="1" s="25">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>MARGALLA ENCLAVE LINK ROAD — EARTHWORK FILL PROGRESS  |  Gross: 898,453 m³  −  Structure: 57,294 m³  =  Net Target: 841,159 m³</t>
         </is>
       </c>
-      <c r="B1" s="25" t="n"/>
-      <c r="C1" s="25" t="n"/>
-      <c r="D1" s="25" t="n"/>
-      <c r="E1" s="25" t="n"/>
-      <c r="F1" s="25" t="n"/>
-      <c r="G1" s="25" t="n"/>
-      <c r="H1" s="26" t="n"/>
-    </row>
-    <row r="2" ht="21.95" customHeight="1" s="23">
+      <c r="B1" s="27" t="n"/>
+      <c r="C1" s="27" t="n"/>
+      <c r="D1" s="27" t="n"/>
+      <c r="E1" s="27" t="n"/>
+      <c r="F1" s="27" t="n"/>
+      <c r="G1" s="27" t="n"/>
+      <c r="H1" s="28" t="n"/>
+    </row>
+    <row r="2" ht="21.95" customHeight="1" s="25">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Contractor</t>
@@ -742,10 +743,10 @@
         <v>242029</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>155843</v>
+        <v>179100</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>4057</v>
+        <v>0</v>
       </c>
       <c r="F3" s="6">
         <f>D3+E3</f>
@@ -778,7 +779,7 @@
         <v>221671</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="F4" s="6">
         <f>D4+E4</f>
@@ -811,7 +812,7 @@
         <v>143371</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -844,7 +845,7 @@
         <v>22480</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1340</v>
+        <v>0</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>
@@ -892,7 +893,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>Structure Deduction: 57,294 m³  →  Net Target: 841,159 m³  |  Work Done: 525,092 m³  |  Net Balance: 316,067 m³  |  Net Progress: 62.4%</t>
         </is>
@@ -916,25 +917,25 @@
   <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="23" min="1" max="1"/>
-    <col width="24" customWidth="1" style="23" min="2" max="2"/>
-    <col width="28" customWidth="1" style="23" min="3" max="3"/>
-    <col width="18" customWidth="1" style="23" min="4" max="4"/>
-    <col width="20" customWidth="1" style="23" min="5" max="5"/>
-    <col width="25" customWidth="1" style="23" min="6" max="6"/>
+    <col width="13" customWidth="1" style="25" min="1" max="1"/>
+    <col width="24" customWidth="1" style="25" min="2" max="2"/>
+    <col width="28" customWidth="1" style="25" min="3" max="3"/>
+    <col width="18" customWidth="1" style="25" min="4" max="4"/>
+    <col width="20" customWidth="1" style="25" min="5" max="5"/>
+    <col width="25" customWidth="1" style="25" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26.1" customHeight="1" s="23">
-      <c r="A1" s="29" t="inlineStr">
+    <row r="1" ht="26.1" customHeight="1" s="25">
+      <c r="A1" s="31" t="inlineStr">
         <is>
           <t>DAILY WORK LOG</t>
         </is>
       </c>
-      <c r="B1" s="25" t="n"/>
-      <c r="C1" s="25" t="n"/>
-      <c r="D1" s="25" t="n"/>
-      <c r="E1" s="25" t="n"/>
-      <c r="F1" s="26" t="n"/>
+      <c r="B1" s="27" t="n"/>
+      <c r="C1" s="27" t="n"/>
+      <c r="D1" s="27" t="n"/>
+      <c r="E1" s="27" t="n"/>
+      <c r="F1" s="28" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1521,196 +1522,196 @@
       <c r="F25" s="20" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>Al Ajal Builders</t>
         </is>
       </c>
-      <c r="C26" s="30" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>Section-1 (0+000 to 1+000)</t>
         </is>
       </c>
-      <c r="D26" s="31" t="n">
+      <c r="D26" s="23" t="n">
         <v>3734</v>
       </c>
-      <c r="E26" s="31" t="n">
+      <c r="E26" s="23" t="n">
         <v>151786</v>
       </c>
-      <c r="F26" s="30" t="inlineStr"/>
+      <c r="F26" s="22" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="B27" s="30" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>BAS Construction</t>
         </is>
       </c>
-      <c r="C27" s="30" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>Section-2 (1+000 to 2+000)</t>
         </is>
       </c>
-      <c r="D27" s="31" t="n">
+      <c r="D27" s="23" t="n">
         <v>3200</v>
       </c>
-      <c r="E27" s="31" t="n">
+      <c r="E27" s="23" t="n">
         <v>217671</v>
       </c>
-      <c r="F27" s="30" t="inlineStr"/>
+      <c r="F27" s="22" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="B28" s="30" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>M. Shehzad Abbasi</t>
         </is>
       </c>
-      <c r="C28" s="30" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>Section-3 (2+000 to 3+000)</t>
         </is>
       </c>
-      <c r="D28" s="31" t="n">
+      <c r="D28" s="23" t="n">
         <v>2850</v>
       </c>
-      <c r="E28" s="31" t="n">
+      <c r="E28" s="23" t="n">
         <v>140171</v>
       </c>
-      <c r="F28" s="30" t="inlineStr"/>
+      <c r="F28" s="22" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="inlineStr">
+      <c r="A29" s="22" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="B29" s="30" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>Fazal Rehman</t>
         </is>
       </c>
-      <c r="C29" s="30" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>Section-4 (3+000 to 3+750)</t>
         </is>
       </c>
-      <c r="D29" s="31" t="n">
+      <c r="D29" s="23" t="n">
         <v>1140</v>
       </c>
-      <c r="E29" s="31" t="n">
+      <c r="E29" s="23" t="n">
         <v>21140</v>
       </c>
-      <c r="F29" s="30" t="inlineStr"/>
+      <c r="F29" s="22" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="B30" s="30" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>Al Ajal Builders</t>
         </is>
       </c>
-      <c r="C30" s="30" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>Section-1 (0+000 to 1+000)</t>
         </is>
       </c>
-      <c r="D30" s="31" t="n">
+      <c r="D30" s="23" t="n">
         <v>4057</v>
       </c>
-      <c r="E30" s="31" t="n">
+      <c r="E30" s="23" t="n">
         <v>155843</v>
       </c>
-      <c r="F30" s="30" t="inlineStr"/>
+      <c r="F30" s="22" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="B31" s="30" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>BAS Construction</t>
         </is>
       </c>
-      <c r="C31" s="30" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>Section-2 (1+000 to 2+000)</t>
         </is>
       </c>
-      <c r="D31" s="31" t="n">
+      <c r="D31" s="23" t="n">
         <v>4000</v>
       </c>
-      <c r="E31" s="31" t="n">
+      <c r="E31" s="23" t="n">
         <v>221671</v>
       </c>
-      <c r="F31" s="30" t="inlineStr"/>
+      <c r="F31" s="22" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="30" t="inlineStr">
+      <c r="A32" s="22" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="B32" s="30" t="inlineStr">
+      <c r="B32" s="22" t="inlineStr">
         <is>
           <t>M. Shehzad Abbasi</t>
         </is>
       </c>
-      <c r="C32" s="30" t="inlineStr">
+      <c r="C32" s="22" t="inlineStr">
         <is>
           <t>Section-3 (2+000 to 3+000)</t>
         </is>
       </c>
-      <c r="D32" s="31" t="n">
+      <c r="D32" s="23" t="n">
         <v>3200</v>
       </c>
-      <c r="E32" s="31" t="n">
+      <c r="E32" s="23" t="n">
         <v>143371</v>
       </c>
-      <c r="F32" s="30" t="inlineStr"/>
+      <c r="F32" s="22" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="B33" s="30" t="inlineStr">
+      <c r="B33" s="22" t="inlineStr">
         <is>
           <t>Fazal Rehman</t>
         </is>
       </c>
-      <c r="C33" s="30" t="inlineStr">
+      <c r="C33" s="22" t="inlineStr">
         <is>
           <t>Section-4 (3+000 to 3+750)</t>
         </is>
       </c>
-      <c r="D33" s="31" t="n">
+      <c r="D33" s="23" t="n">
         <v>1340</v>
       </c>
-      <c r="E33" s="31" t="n">
+      <c r="E33" s="23" t="n">
         <v>22480</v>
       </c>
-      <c r="F33" s="30" t="inlineStr"/>
+      <c r="F33" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -205,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -280,17 +280,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -673,7 +667,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26.1" customHeight="1" s="25">
-      <c r="A1" s="30" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>MARGALLA ENCLAVE LINK ROAD — EARTHWORK FILL PROGRESS  |  Gross: 898,453 m³  −  Structure: 57,294 m³  =  Net Target: 841,159 m³</t>
         </is>
@@ -743,7 +737,7 @@
         <v>242029</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>179100</v>
+        <v>183157</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
@@ -776,7 +770,7 @@
         <v>349638</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>221671</v>
+        <v>194806</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>0</v>
@@ -926,7 +920,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26.1" customHeight="1" s="25">
-      <c r="A1" s="31" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>DAILY WORK LOG</t>
         </is>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -836,7 +836,7 @@
         <v>97000</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>22480</v>
+        <v>24082</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -51,7 +51,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -103,8 +103,13 @@
         <fgColor rgb="FFFFFDE7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFDE7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -201,11 +206,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00AAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="00AAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="00AAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00AAAAAA"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -286,6 +305,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="11" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -737,10 +762,10 @@
         <v>242029</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>183157</v>
+        <v>186657</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>3500</v>
       </c>
       <c r="F3" s="6">
         <f>D3+E3</f>
@@ -770,10 +795,10 @@
         <v>349638</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>194806</v>
+        <v>197806</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F4" s="6">
         <f>D4+E4</f>
@@ -803,10 +828,10 @@
         <v>211523</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>143371</v>
+        <v>145871</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -836,10 +861,10 @@
         <v>97000</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>24082</v>
+        <v>24882</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>
@@ -908,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="25" min="1" max="1"/>
@@ -1707,6 +1732,102 @@
       </c>
       <c r="F33" s="22" t="n"/>
     </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>Al Ajal Builders</t>
+        </is>
+      </c>
+      <c r="C34" s="30" t="inlineStr">
+        <is>
+          <t>Section-1 (0+000 to 1+000)</t>
+        </is>
+      </c>
+      <c r="D34" s="31" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E34" s="31" t="n">
+        <v>186657</v>
+      </c>
+      <c r="F34" s="30" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>BAS Construction</t>
+        </is>
+      </c>
+      <c r="C35" s="30" t="inlineStr">
+        <is>
+          <t>Section-2 (1+000 to 2+000)</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E35" s="31" t="n">
+        <v>197806</v>
+      </c>
+      <c r="F35" s="30" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>M. Shehzad Abbasi</t>
+        </is>
+      </c>
+      <c r="C36" s="30" t="inlineStr">
+        <is>
+          <t>Section-3 (2+000 to 3+000)</t>
+        </is>
+      </c>
+      <c r="D36" s="31" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E36" s="31" t="n">
+        <v>145871</v>
+      </c>
+      <c r="F36" s="30" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>Fazal Rehman</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
+          <t>Section-4 (3+000 to 3+750)</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="n">
+        <v>800</v>
+      </c>
+      <c r="E37" s="31" t="n">
+        <v>24882</v>
+      </c>
+      <c r="F37" s="30" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/Road_Data.xlsx
+++ b/Road_Data.xlsx
@@ -762,7 +762,7 @@
         <v>242029</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>186657</v>
+        <v>190157</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>3500</v>
@@ -795,10 +795,10 @@
         <v>349638</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>197806</v>
+        <v>201006</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="F4" s="6">
         <f>D4+E4</f>
@@ -828,10 +828,10 @@
         <v>211523</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>145871</v>
+        <v>148471</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="F5" s="6">
         <f>D5+E5</f>
@@ -861,10 +861,10 @@
         <v>97000</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>24882</v>
+        <v>25732</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>800</v>
+        <v>850</v>
       </c>
       <c r="F6" s="6">
         <f>D6+E6</f>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="25" min="1" max="1"/>
@@ -1828,6 +1828,102 @@
       </c>
       <c r="F37" s="30" t="inlineStr"/>
     </row>
+    <row r="38">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B38" s="30" t="inlineStr">
+        <is>
+          <t>Al Ajal Builders</t>
+        </is>
+      </c>
+      <c r="C38" s="30" t="inlineStr">
+        <is>
+          <t>Section-1 (0+000 to 1+000)</t>
+        </is>
+      </c>
+      <c r="D38" s="31" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E38" s="31" t="n">
+        <v>190157</v>
+      </c>
+      <c r="F38" s="30" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B39" s="30" t="inlineStr">
+        <is>
+          <t>BAS Construction</t>
+        </is>
+      </c>
+      <c r="C39" s="30" t="inlineStr">
+        <is>
+          <t>Section-2 (1+000 to 2+000)</t>
+        </is>
+      </c>
+      <c r="D39" s="31" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E39" s="31" t="n">
+        <v>201006</v>
+      </c>
+      <c r="F39" s="30" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B40" s="30" t="inlineStr">
+        <is>
+          <t>M. Shehzad Abbasi</t>
+        </is>
+      </c>
+      <c r="C40" s="30" t="inlineStr">
+        <is>
+          <t>Section-3 (2+000 to 3+000)</t>
+        </is>
+      </c>
+      <c r="D40" s="31" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E40" s="31" t="n">
+        <v>148471</v>
+      </c>
+      <c r="F40" s="30" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B41" s="30" t="inlineStr">
+        <is>
+          <t>Fazal Rehman</t>
+        </is>
+      </c>
+      <c r="C41" s="30" t="inlineStr">
+        <is>
+          <t>Section-4 (3+000 to 3+750)</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>850</v>
+      </c>
+      <c r="E41" s="31" t="n">
+        <v>25732</v>
+      </c>
+      <c r="F41" s="30" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
